--- a/基本設計/08_日報と通知_画面基本設計書.xlsx
+++ b/基本設計/08_日報と通知_画面基本設計書.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R2e2b7cd307bd4e8f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R2c16c5c891cb4e33"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_画面一覧" sheetId="13" r:id="Re596c1849e8c480d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_画面遷移" sheetId="14" r:id="R48c33369d5ad496b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_画面項目定義" sheetId="16" r:id="R9e2ef5b4a6bc4bbd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_画面処理概要" sheetId="18" r:id="Re33a491341b14b23"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-019_マイ日報" sheetId="19" r:id="Reb18a4e251f340f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-020_日報登録" sheetId="20" r:id="R7ba523761da0486b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-021_日報検索" sheetId="21" r:id="R292ec3d2ddfe44ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-022_通知一覧" sheetId="22" r:id="R16ad5c728ca74c4a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R750e8fefe402445e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Ra6aa596e5f4249a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_画面一覧" sheetId="13" r:id="R5ae10912b3c24145"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_画面遷移" sheetId="14" r:id="R16a59e6ca8be416f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_画面項目定義" sheetId="16" r:id="Re9eaf4494e2f4b82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_画面処理概要" sheetId="18" r:id="R26a2a15d36934098"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-019_マイ日報" sheetId="19" r:id="Rd6ae43dab0794135"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-020_日報登録" sheetId="20" r:id="R19561a68b9b64fab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-021_日報検索" sheetId="21" r:id="Rd731537e9397459b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-022_通知一覧" sheetId="22" r:id="Rb84c55ee1b1a4d0a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1660,10 +1660,7 @@
       <x:c r="F16" s="287"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" t="str">
-        <x:v>本書は Company WorkHub の基本設計内容を定義する。
-Ver.1.8 は状態変更入口、API/DB制約、取込Transaction、日報一意制約、通知・Token保持を整合した再Review対応版である。</x:v>
-      </x:c>
+      <x:c r="A17"/>
       <x:c r="C17"/>
       <x:c r="D17"/>
       <x:c r="E17"/>
@@ -1678,25 +1675,22 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19"/>
-      <x:c r="B19" s="330" t="str">
-        <x:v>本書は Company WorkHub の基本設計内容を定義する。
-Ver.1.7 は状態変更入口、API/DB制約、取込Transaction、日報一意制約、通知・Token保持を整合した再Review対応版である。</x:v>
-      </x:c>
-      <x:c r="C19" s="330"/>
-      <x:c r="D19" s="330"/>
-      <x:c r="E19" s="330"/>
-      <x:c r="F19" s="330"/>
-      <x:c r="G19" s="330"/>
-      <x:c r="H19" s="330"/>
+      <x:c r="B19"/>
+      <x:c r="C19"/>
+      <x:c r="D19"/>
+      <x:c r="E19"/>
+      <x:c r="F19"/>
+      <x:c r="G19"/>
+      <x:c r="H19"/>
     </x:row>
     <x:row r="20">
-      <x:c r="B20" s="330"/>
-      <x:c r="C20" s="330"/>
-      <x:c r="D20" s="330"/>
-      <x:c r="E20" s="330"/>
-      <x:c r="F20" s="330"/>
-      <x:c r="G20" s="330"/>
-      <x:c r="H20" s="330"/>
+      <x:c r="B20"/>
+      <x:c r="C20"/>
+      <x:c r="D20"/>
+      <x:c r="E20"/>
+      <x:c r="F20"/>
+      <x:c r="G20"/>
+      <x:c r="H20"/>
     </x:row>
     <x:row r="21">
       <x:c r="B21" s="330"/>
@@ -3302,54 +3296,22 @@
       <x:c r="P31" s="48"/>
     </x:row>
     <x:row r="32" ht="21" customHeight="1">
-      <x:c r="A32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="B32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="C32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="D32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="E32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="F32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="G32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="H32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="I32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="J32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="K32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="L32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="M32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="N32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="O32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="P32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
+      <x:c r="A32"/>
+      <x:c r="B32"/>
+      <x:c r="C32"/>
+      <x:c r="D32"/>
+      <x:c r="E32"/>
+      <x:c r="F32"/>
+      <x:c r="G32"/>
+      <x:c r="H32"/>
+      <x:c r="I32"/>
+      <x:c r="J32"/>
+      <x:c r="K32"/>
+      <x:c r="L32"/>
+      <x:c r="M32"/>
+      <x:c r="N32"/>
+      <x:c r="O32"/>
+      <x:c r="P32"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -8794,54 +8756,22 @@
       <x:c r="P31" s="48"/>
     </x:row>
     <x:row r="32" ht="21" customHeight="1">
-      <x:c r="A32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="B32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="C32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="D32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="E32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="F32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="G32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="H32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="I32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="J32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="K32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="L32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="M32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="N32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="O32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="P32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
+      <x:c r="A32"/>
+      <x:c r="B32"/>
+      <x:c r="C32"/>
+      <x:c r="D32"/>
+      <x:c r="E32"/>
+      <x:c r="F32"/>
+      <x:c r="G32"/>
+      <x:c r="H32"/>
+      <x:c r="I32"/>
+      <x:c r="J32"/>
+      <x:c r="K32"/>
+      <x:c r="L32"/>
+      <x:c r="M32"/>
+      <x:c r="N32"/>
+      <x:c r="O32"/>
+      <x:c r="P32"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -10412,54 +10342,22 @@
       <x:c r="P31" s="48"/>
     </x:row>
     <x:row r="32" ht="21" customHeight="1">
-      <x:c r="A32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="B32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="C32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="D32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="E32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="F32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="G32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="H32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="I32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="J32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="K32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="L32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="M32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="N32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="O32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="P32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
+      <x:c r="A32"/>
+      <x:c r="B32"/>
+      <x:c r="C32"/>
+      <x:c r="D32"/>
+      <x:c r="E32"/>
+      <x:c r="F32"/>
+      <x:c r="G32"/>
+      <x:c r="H32"/>
+      <x:c r="I32"/>
+      <x:c r="J32"/>
+      <x:c r="K32"/>
+      <x:c r="L32"/>
+      <x:c r="M32"/>
+      <x:c r="N32"/>
+      <x:c r="O32"/>
+      <x:c r="P32"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -12055,54 +11953,22 @@
       <x:c r="P31" s="48"/>
     </x:row>
     <x:row r="32" ht="21" customHeight="1">
-      <x:c r="A32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="B32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="C32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="D32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="E32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="F32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="G32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="H32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="I32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="J32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="K32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="L32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="M32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="N32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="O32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="P32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
+      <x:c r="A32"/>
+      <x:c r="B32"/>
+      <x:c r="C32"/>
+      <x:c r="D32"/>
+      <x:c r="E32"/>
+      <x:c r="F32"/>
+      <x:c r="G32"/>
+      <x:c r="H32"/>
+      <x:c r="I32"/>
+      <x:c r="J32"/>
+      <x:c r="K32"/>
+      <x:c r="L32"/>
+      <x:c r="M32"/>
+      <x:c r="N32"/>
+      <x:c r="O32"/>
+      <x:c r="P32"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
